--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,39 +470,88 @@
           <t>n_failed</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>model_role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe</t>
+          <t>logit_elasticnet_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8810525664936373</v>
+        <v>0.8811585985239313</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004399871941074101</v>
+        <v>0.004389213114772924</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7000061433590246</v>
+        <v>0.697863011313659</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005493287863198479</v>
+        <v>0.005226812006440109</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8419347122034452</v>
+        <v>0.7936804073504355</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003374486507193572</v>
+        <v>0.007895207356770791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5959828291514137</v>
+        <v>0.643112712468934</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01093835291011654</v>
+        <v>0.01065785074699211</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random_classifier</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5018559714056471</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.001720555585391747</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2279191500425641</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0006133047160225449</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6535903477494552</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00121384248121297</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2269038960423601</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.002692826940019715</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -516,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,11 +619,16 @@
           <t>n_rows</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>model_role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe</t>
+          <t>logit_elasticnet_binned_ohe_balanced</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -583,28 +637,74 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8766855123348262</v>
+        <v>0.8771380317718289</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6951580607241479</v>
+        <v>0.6933499882637983</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8424338345203553</v>
+        <v>0.7898971247691902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.598116169544741</v>
+        <v>0.6373226075738029</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7115795090715048</v>
+        <v>0.524416135881104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5158607350096712</v>
+        <v>0.8121856866537718</v>
       </c>
       <c r="I2" t="n">
         <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random_classifier</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5046975544284495</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2289951995767124</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6513672733667458</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2351466049382716</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2345132743362832</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2357833655705996</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22746</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -618,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,50 +769,203 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>median_ape</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>median_ape_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>n_failed</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>median_ape</t>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>model_role</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>classic_linear_standard_scaler</t>
+          <t>xgboost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.134305440365721</v>
+        <v>0.1556449308072873</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005908956821955524</v>
+        <v>0.008168964458105639</v>
       </c>
       <c r="D2" t="n">
-        <v>74262.72147331353</v>
+        <v>72293.14848528159</v>
       </c>
       <c r="E2" t="n">
-        <v>1070.54070351209</v>
+        <v>922.4753062340619</v>
       </c>
       <c r="F2" t="n">
-        <v>15575596417.10759</v>
+        <v>15192232416.66863</v>
       </c>
       <c r="G2" t="n">
-        <v>870719069.2563313</v>
+        <v>866745755.1855794</v>
       </c>
       <c r="H2" t="n">
-        <v>297.0911311089059</v>
+        <v>294.5538742385909</v>
       </c>
       <c r="I2" t="n">
-        <v>54.85963670912852</v>
+        <v>54.53461770996989</v>
       </c>
       <c r="J2" t="n">
+        <v>0.7773382067680359</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.007473604843902352</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.7893165012410386</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mean_regressor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.0001604638596926389</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0001217442387676462</v>
+      </c>
+      <c r="D3" t="n">
+        <v>84933.14754427197</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1278.344049836328</v>
+      </c>
+      <c r="F3" t="n">
+        <v>17995185275.5386</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1009063682.08735</v>
+      </c>
+      <c r="H3" t="n">
+        <v>235.0399495657002</v>
+      </c>
+      <c r="I3" t="n">
+        <v>53.88888012653806</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8829624687500001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.007611817593881241</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>median_regressor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.1083769211496982</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.002159443703462797</v>
+      </c>
+      <c r="D4" t="n">
+        <v>75011.173410296</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1494.78183942886</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19943194831.72226</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1139733945.430216</v>
+      </c>
+      <c r="H4" t="n">
+        <v>124.7104595910728</v>
+      </c>
+      <c r="I4" t="n">
+        <v>28.44224996650644</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7462414725535839</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.008404322865485285</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>random_regressor</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-1.053439423531181</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0569242886524596</v>
+      </c>
+      <c r="D5" t="n">
+        <v>115041.0624527173</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2091.856279170782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>36908630285.07372</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1368710206.121246</v>
+      </c>
+      <c r="H5" t="n">
+        <v>164.0865786876999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>65.34359371801101</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.903809739193137</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.006508540706215832</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -726,7 +979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,11 +1028,16 @@
           <t>n_rows</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>model_role</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>classic_linear_standard_scaler</t>
+          <t>xgboost</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -788,26 +1046,137 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1352983069629075</v>
+        <v>0.1612625884584747</v>
       </c>
       <c r="D2" t="n">
-        <v>74024.11594950108</v>
+        <v>71850.76404367684</v>
       </c>
       <c r="E2" t="n">
-        <v>15466867635.33347</v>
+        <v>15002446080.04776</v>
       </c>
       <c r="F2" t="n">
-        <v>124365.86201741</v>
+        <v>122484.4728120579</v>
       </c>
       <c r="G2" t="n">
-        <v>298.5999415606234</v>
+        <v>303.6279495810064</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7852474459179121</v>
+        <v>0.76895146484375</v>
       </c>
       <c r="I2" t="n">
         <v>22746</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>random_regressor</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.9722540815959906</v>
+      </c>
+      <c r="D3" t="n">
+        <v>113392.1273190891</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35277591184.24998</v>
+      </c>
+      <c r="F3" t="n">
+        <v>187823.2977674761</v>
+      </c>
+      <c r="G3" t="n">
+        <v>220.0608754496749</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.900990099009901</v>
+      </c>
+      <c r="I3" t="n">
+        <v>22746</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mean_regressor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.201258216676493e-06</v>
+      </c>
+      <c r="D4" t="n">
+        <v>84921.64665215863</v>
+      </c>
+      <c r="E4" t="n">
+        <v>17886961873.18767</v>
+      </c>
+      <c r="F4" t="n">
+        <v>133742.1469589436</v>
+      </c>
+      <c r="G4" t="n">
+        <v>242.1543537500807</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.88296265625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>22746</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>median_regressor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.1082430123076936</v>
+      </c>
+      <c r="D5" t="n">
+        <v>74891.72522641343</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19823076694.74061</v>
+      </c>
+      <c r="F5" t="n">
+        <v>140794.4483803982</v>
+      </c>
+      <c r="G5" t="n">
+        <v>128.5085101399455</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22746</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="classification_test" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="regression_cv" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="regression_test" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cls_optimal_threshold" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,32 +480,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8811585985239313</v>
+        <v>0.881130493247186</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004389213114772924</v>
+        <v>0.004370391028659821</v>
       </c>
       <c r="D2" t="n">
-        <v>0.697863011313659</v>
+        <v>0.6980576057044253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005226812006440109</v>
+        <v>0.005206617861945132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7936804073504355</v>
+        <v>0.8403330948442059</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007895207356770791</v>
+        <v>0.002963045688369091</v>
       </c>
       <c r="H2" t="n">
-        <v>0.643112712468934</v>
+        <v>0.5876274656093299</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01065785074699211</v>
+        <v>0.01020369228274071</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -628,7 +629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_elasticnet_binned_ohe_balanced</t>
+          <t>logit_binned_ohe_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,22 +638,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8771380317718289</v>
+        <v>0.8771122911143998</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6933499882637983</v>
+        <v>0.6933517849967762</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7898971247691902</v>
+        <v>0.8415105952694979</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6373226075738029</v>
+        <v>0.5938943336712853</v>
       </c>
       <c r="G2" t="n">
-        <v>0.524416135881104</v>
+        <v>0.7110871324521176</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8121856866537718</v>
+        <v>0.5098646034816248</v>
       </c>
       <c r="I2" t="n">
         <v>0.5</v>
@@ -1142,7 +1143,6 @@
       <c r="I4" t="n">
         <v>22746</v>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1176,7 +1176,170 @@
       <c r="I5" t="n">
         <v>22746</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Selected @ optimal threshold</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3140000487021511</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8199683460828278</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5840763334897544</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7222437137330754</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.645853152296117</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14917</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2659</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1436</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Random classifier</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0.6513672733667458</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2345132743362832</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2357833655705996</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2351466049382716</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13597</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3979</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3951</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Always true</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0.2272927108062956</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2272927108062956</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3703969050007164</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17576</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5170</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -792,38 +792,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>xgboost</t>
+          <t>xgboost_boxcox</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1556449308072873</v>
+        <v>0.0623203668740866</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008168964458105639</v>
+        <v>0.01031224401544338</v>
       </c>
       <c r="D2" t="n">
-        <v>72293.14848528159</v>
+        <v>65098.04976889039</v>
       </c>
       <c r="E2" t="n">
-        <v>922.4753062340619</v>
+        <v>1511.137115055378</v>
       </c>
       <c r="F2" t="n">
-        <v>15192232416.66863</v>
+        <v>16876798731.90952</v>
       </c>
       <c r="G2" t="n">
-        <v>866745755.1855794</v>
+        <v>1078923491.315051</v>
       </c>
       <c r="H2" t="n">
-        <v>294.5538742385909</v>
+        <v>164.1180190717068</v>
       </c>
       <c r="I2" t="n">
-        <v>54.53461770996989</v>
+        <v>31.21398598868741</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7773382067680359</v>
+        <v>0.6172423362731934</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007473604843902352</v>
+        <v>0.008209914468147367</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -837,38 +837,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mean_regressor</t>
+          <t>median_regressor</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0001604638596926389</v>
+        <v>-0.1083769211496982</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001217442387676462</v>
+        <v>0.002159443703462797</v>
       </c>
       <c r="D3" t="n">
-        <v>84933.14754427197</v>
+        <v>75011.173410296</v>
       </c>
       <c r="E3" t="n">
-        <v>1278.344049836328</v>
+        <v>1494.78183942886</v>
       </c>
       <c r="F3" t="n">
-        <v>17995185275.5386</v>
+        <v>19943194831.72226</v>
       </c>
       <c r="G3" t="n">
-        <v>1009063682.08735</v>
+        <v>1139733945.430216</v>
       </c>
       <c r="H3" t="n">
-        <v>235.0399495657002</v>
+        <v>124.7104595910728</v>
       </c>
       <c r="I3" t="n">
-        <v>53.88888012653806</v>
+        <v>28.44224996650644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8829624687500001</v>
+        <v>0.7462414725535839</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007611817593881241</v>
+        <v>0.008404322865485285</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -882,38 +882,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>median_regressor</t>
+          <t>mean_regressor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1083769211496982</v>
+        <v>-0.0001604638596926389</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002159443703462797</v>
+        <v>0.0001217442387676462</v>
       </c>
       <c r="D4" t="n">
-        <v>75011.173410296</v>
+        <v>84933.14754427197</v>
       </c>
       <c r="E4" t="n">
-        <v>1494.78183942886</v>
+        <v>1278.344049836328</v>
       </c>
       <c r="F4" t="n">
-        <v>19943194831.72226</v>
+        <v>17995185275.5386</v>
       </c>
       <c r="G4" t="n">
-        <v>1139733945.430216</v>
+        <v>1009063682.08735</v>
       </c>
       <c r="H4" t="n">
-        <v>124.7104595910728</v>
+        <v>235.0399495657002</v>
       </c>
       <c r="I4" t="n">
-        <v>28.44224996650644</v>
+        <v>53.88888012653806</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7462414725535839</v>
+        <v>0.8829624687500001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008404322865485285</v>
+        <v>0.007611817593881241</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>xgboost</t>
+          <t>xgboost_boxcox</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1047,22 +1047,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1612625884584747</v>
+        <v>0.06744429869476365</v>
       </c>
       <c r="D2" t="n">
-        <v>71850.76404367684</v>
+        <v>64992.90788129644</v>
       </c>
       <c r="E2" t="n">
-        <v>15002446080.04776</v>
+        <v>16680568236.2009</v>
       </c>
       <c r="F2" t="n">
-        <v>122484.4728120579</v>
+        <v>129153.2741985309</v>
       </c>
       <c r="G2" t="n">
-        <v>303.6279495810064</v>
+        <v>172.8593948797542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.76895146484375</v>
+        <v>0.6149460286458333</v>
       </c>
       <c r="I2" t="n">
         <v>22746</v>

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,20 +458,40 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>precision_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>precision_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>recall_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>recall_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>f1_mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>f1_std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_failed</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>model_role</t>
         </is>
@@ -502,15 +522,27 @@
         <v>0.002963045688369091</v>
       </c>
       <c r="H2" t="n">
+        <v>0.7111746540752869</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.006902739266586057</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5007047577418887</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01202107305064498</v>
+      </c>
+      <c r="L2" t="n">
         <v>0.5876274656093299</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>0.01020369228274071</v>
       </c>
-      <c r="J2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>selected</t>
         </is>
@@ -541,15 +573,27 @@
         <v>0.00121384248121297</v>
       </c>
       <c r="H3" t="n">
+        <v>0.2302047781569966</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.002725037444141857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2236963407853673</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.002661475279300156</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.2269038960423601</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>0.002692826940019715</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>baseline</t>
         </is>

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -500,44 +500,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.881130493247186</v>
+        <v>0.9140224688816492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004370391028659821</v>
+        <v>0.004096515051063659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6980576057044253</v>
+        <v>0.7727977418390275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005206617861945132</v>
+        <v>0.01129734405204536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8403330948442059</v>
+        <v>0.8472481097273652</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002963045688369091</v>
+        <v>0.005891976215397637</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7111746540752869</v>
+        <v>0.6269140050499862</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006902739266586057</v>
+        <v>0.01131547974546328</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5007047577418887</v>
+        <v>0.810131034288428</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01202107305064498</v>
+        <v>0.006975526899547858</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5876274656093299</v>
+        <v>0.7068293562382115</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01020369228274071</v>
+        <v>0.009790777061447854</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>logit_binned_ohe_balanced_calibrated</t>
+          <t>random_forest_classifier_balanced</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -682,25 +682,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8771122911143998</v>
+        <v>0.9116048160891104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6933517849967762</v>
+        <v>0.7693212731610033</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8415105952694979</v>
+        <v>0.8614261848237053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5938943336712853</v>
+        <v>0.7076066790352504</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7110871324521176</v>
+        <v>0.6798573975044563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5098646034816248</v>
+        <v>0.7377176015473887</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.5806481666978933</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -1294,31 +1294,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3140000487021511</v>
+        <v>0.5806481666978933</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8199683460828278</v>
+        <v>0.8614261848237053</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5840763334897544</v>
+        <v>0.6798573975044563</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7222437137330754</v>
+        <v>0.7377176015473887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.645853152296117</v>
+        <v>0.7076066790352504</v>
       </c>
       <c r="G2" t="n">
-        <v>14917</v>
+        <v>15780</v>
       </c>
       <c r="H2" t="n">
-        <v>2659</v>
+        <v>1796</v>
       </c>
       <c r="I2" t="n">
-        <v>1436</v>
+        <v>1356</v>
       </c>
       <c r="J2" t="n">
-        <v>3734</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="3">

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -500,44 +500,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9140224688816492</v>
+        <v>0.9119921166430066</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004096515051063659</v>
+        <v>0.00399088077855746</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7727977418390275</v>
+        <v>0.7668162634417706</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01129734405204536</v>
+        <v>0.01115278984033312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8472481097273652</v>
+        <v>0.868746815522225</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005891976215397637</v>
+        <v>0.003644794072609333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6269140050499862</v>
+        <v>0.7324243310589672</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01131547974546328</v>
+        <v>0.01090800262412072</v>
       </c>
       <c r="J2" t="n">
-        <v>0.810131034288428</v>
+        <v>0.6657820855660914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006975526899547858</v>
+        <v>0.008829824930161092</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7068293562382115</v>
+        <v>0.6974760717590649</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009790777061447854</v>
+        <v>0.007879200146788794</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_forest_classifier_balanced</t>
+          <t>random_forest_classifier_balanced_calibrated</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -682,25 +682,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9116048160891104</v>
+        <v>0.9093468740123026</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7693212731610033</v>
+        <v>0.7624737774930801</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8614261848237053</v>
+        <v>0.8600193440604942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7076066790352504</v>
+        <v>0.7053488802517121</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6798573975044563</v>
+        <v>0.6761887863733144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7377176015473887</v>
+        <v>0.7371373307543521</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5806481666978933</v>
+        <v>0.3937199960935918</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -1294,31 +1294,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5806481666978933</v>
+        <v>0.3937199960935918</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8614261848237053</v>
+        <v>0.8600193440604942</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6798573975044563</v>
+        <v>0.6761887863733144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7377176015473887</v>
+        <v>0.7371373307543521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7076066790352504</v>
+        <v>0.7053488802517121</v>
       </c>
       <c r="G2" t="n">
-        <v>15780</v>
+        <v>15751</v>
       </c>
       <c r="H2" t="n">
-        <v>1796</v>
+        <v>1825</v>
       </c>
       <c r="I2" t="n">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="J2" t="n">
-        <v>3814</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="3">

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -504,40 +504,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9119921166430066</v>
+        <v>0.9119067937133698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00399088077855746</v>
+        <v>0.004023626536093945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7668162634417706</v>
+        <v>0.7665254818664221</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01115278984033312</v>
+        <v>0.01153895645575349</v>
       </c>
       <c r="F2" t="n">
-        <v>0.868746815522225</v>
+        <v>0.8687845051474865</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003644794072609333</v>
+        <v>0.003772569022227441</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7324243310589672</v>
+        <v>0.7323542393028306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01090800262412072</v>
+        <v>0.01126666485400947</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6657820855660914</v>
+        <v>0.6661965074475666</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008829824930161092</v>
+        <v>0.009519772006363208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6974760717590649</v>
+        <v>0.6976658253851086</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007879200146788794</v>
+        <v>0.008233140636698871</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -682,25 +682,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9093468740123026</v>
+        <v>0.9094663881378598</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7624737774930801</v>
+        <v>0.7632744530484556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8600193440604942</v>
+        <v>0.8209355491075354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7053488802517121</v>
+        <v>0.3853930888788291</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6761887863733144</v>
+        <v>0.876458476321208</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7371373307543521</v>
+        <v>0.2470019342359768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3937199960935918</v>
+        <v>0.8157897839479512</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -1294,31 +1294,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3937199960935918</v>
+        <v>0.8157897839479512</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8600193440604942</v>
+        <v>0.8209355491075354</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6761887863733144</v>
+        <v>0.876458476321208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7371373307543521</v>
+        <v>0.2470019342359768</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7053488802517121</v>
+        <v>0.3853930888788291</v>
       </c>
       <c r="G2" t="n">
-        <v>15751</v>
+        <v>17396</v>
       </c>
       <c r="H2" t="n">
-        <v>1825</v>
+        <v>180</v>
       </c>
       <c r="I2" t="n">
-        <v>1359</v>
+        <v>3893</v>
       </c>
       <c r="J2" t="n">
-        <v>3811</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="3">

--- a/slidedeck/data/model_metric_tables.xlsx
+++ b/slidedeck/data/model_metric_tables.xlsx
@@ -688,19 +688,19 @@
         <v>0.7632744530484556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8209355491075354</v>
+        <v>0.8582168293326299</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3853930888788291</v>
+        <v>0.7055063464523788</v>
       </c>
       <c r="G2" t="n">
-        <v>0.876458476321208</v>
+        <v>0.6682234907455458</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2470019342359768</v>
+        <v>0.7471953578336558</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8157897839479512</v>
+        <v>0.3783092077038575</v>
       </c>
       <c r="J2" t="n">
         <v>22746</v>
@@ -1294,31 +1294,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8157897839479512</v>
+        <v>0.3783092077038575</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8209355491075354</v>
+        <v>0.8582168293326299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.876458476321208</v>
+        <v>0.6682234907455458</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2470019342359768</v>
+        <v>0.7471953578336558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3853930888788291</v>
+        <v>0.7055063464523788</v>
       </c>
       <c r="G2" t="n">
-        <v>17396</v>
+        <v>15658</v>
       </c>
       <c r="H2" t="n">
-        <v>180</v>
+        <v>1918</v>
       </c>
       <c r="I2" t="n">
-        <v>3893</v>
+        <v>1307</v>
       </c>
       <c r="J2" t="n">
-        <v>1277</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="3">
